--- a/conf-data/excel/Datas/quest/quest.xlsx
+++ b/conf-data/excel/Datas/quest/quest.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\opensrc\c++\gameSrv\conf-data\excel\Datas\quest\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733645B2-7898-4637-8E63-447B259D3FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28695" windowHeight="13065" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="index" sheetId="1" r:id="rId1"/>
@@ -21,25 +15,25 @@
     <sheet name="quest_step" sheetId="6" r:id="rId6"/>
     <sheet name="questGlobalVar" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="O4" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="等线"/>
-            <charset val="134"/>
             <scheme val="minor"/>
+            <charset val="0"/>
           </rPr>
           <t>作者:
 控制任务状态变更时，侧边的通知是否显示</t>
@@ -51,66 +45,66 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>zhouyijie</author>
     <author>张明熙</author>
   </authors>
   <commentList>
-    <comment ref="M4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
+    <comment ref="M4" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="等线"/>
-            <charset val="134"/>
             <scheme val="minor"/>
+            <charset val="0"/>
           </rPr>
           <t>zhouyijie:
 目标组或的情况下只显示目标概览，和的情况下才显示目标描述</t>
         </r>
       </text>
     </comment>
-    <comment ref="X4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
+    <comment ref="X4" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="等线"/>
-            <charset val="134"/>
             <scheme val="minor"/>
+            <charset val="0"/>
           </rPr>
           <t>张明熙:
 任务完成后，使整个父任务变为完成状态</t>
         </r>
       </text>
     </comment>
-    <comment ref="Y4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
+    <comment ref="Y4" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="等线"/>
-            <charset val="134"/>
             <scheme val="minor"/>
+            <charset val="0"/>
           </rPr>
           <t>张明熙:
 任务失败后，提示“任务失败”</t>
         </r>
       </text>
     </comment>
-    <comment ref="Z4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
+    <comment ref="Z4" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="等线"/>
-            <charset val="134"/>
             <scheme val="minor"/>
+            <charset val="0"/>
           </rPr>
           <t>张明熙:
 任务完成到一半时下线，再上线时需要恢复到的存档点，以该子任务已完成为存档点</t>
@@ -122,20 +116,20 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="B4" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="等线"/>
-            <charset val="134"/>
             <scheme val="minor"/>
+            <charset val="0"/>
           </rPr>
           <t>作者:
 10000+ 主线任务
@@ -146,15 +140,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
+    <comment ref="D4" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
+            <color rgb="FF000000"/>
             <rFont val="等线"/>
-            <charset val="134"/>
             <scheme val="minor"/>
+            <charset val="0"/>
           </rPr>
           <t xml:space="preserve">作者:
 int类型, 不填为0
@@ -167,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642">
   <si>
     <t>##var</t>
   </si>
@@ -1422,6 +1416,9 @@
     <t>type</t>
   </si>
   <si>
+    <t>variants</t>
+  </si>
+  <si>
     <t>分割符</t>
   </si>
   <si>
@@ -2095,17 +2092,19 @@
   </si>
   <si>
     <t>1.5家园活动是否完成引导任务 0未完成 1完成</t>
-  </si>
-  <si>
-    <t>variants</t>
-    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2117,28 +2116,24 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2146,7 +2141,6 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2154,7 +2148,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2163,7 +2156,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2172,34 +2164,133 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2226,7 +2317,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2238,31 +2329,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.398846400341807"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799340800195319"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39884640034180729"/>
+        <fgColor theme="8" tint="0.799340800195319"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7993408001953185"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2272,8 +2363,176 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2346,26 +2605,256 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2382,166 +2871,193 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="1" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="3" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="7" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="31" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="2">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="31">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="10" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="10"/>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="60% - 着色 2" xfId="4" builtinId="36"/>
-    <cellStyle name="差" xfId="3" builtinId="27"/>
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
-    <cellStyle name="好" xfId="2" builtinId="26"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2559,106 +3075,11 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2916,14 +3337,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="9" style="42" customWidth="1"/>
     <col min="2" max="2" width="25.625" style="42" customWidth="1"/>
@@ -2937,97 +3358,97 @@
     <col min="12" max="16384" width="9" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="51" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+    <row r="1" s="56" customFormat="1" spans="1:11">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="56" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="51" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+    <row r="2" s="56" customFormat="1" spans="1:11">
+      <c r="A2" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="56" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="51" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="51" t="s">
+    <row r="3" s="56" customFormat="1" spans="1:11">
+      <c r="A3" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="56" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5">
       <c r="B4" s="42" t="s">
         <v>27</v>
       </c>
@@ -3037,11 +3458,11 @@
       <c r="D4" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="57" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:5">
       <c r="B5" s="42" t="s">
         <v>30</v>
       </c>
@@ -3051,11 +3472,11 @@
       <c r="D5" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="57" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:7">
       <c r="B6" s="42" t="s">
         <v>33</v>
       </c>
@@ -3065,7 +3486,7 @@
       <c r="D6" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="58" t="s">
         <v>35</v>
       </c>
       <c r="F6" s="42" t="s">
@@ -3073,7 +3494,7 @@
       </c>
       <c r="G6" s="46"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5">
       <c r="B7" s="42" t="s">
         <v>37</v>
       </c>
@@ -3083,29 +3504,30 @@
       <c r="D7" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="57" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E8" s="52"/>
+    <row r="8" spans="5:5">
+      <c r="E8" s="57"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E5" r:id="rId2" tooltip="mailto:quest@quest/quest.xlsx,quest@quest/Levelquest.xlsx" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E4" r:id="rId1" display="chapter@quest/quest.xlsx,chapter@quest/Levelquest.xlsx"/>
+    <hyperlink ref="E5" r:id="rId2" display="quest@quest/quest.xlsx,quest@quest/Levelquest.xlsx" tooltip="mailto:quest@quest/quest.xlsx,quest@quest/Levelquest.xlsx"/>
+    <hyperlink ref="E6" r:id="rId3" display="quest_step@quest/quest.xlsx"/>
+    <hyperlink ref="E7" r:id="rId4" display="questGlobalVar@quest/quest.xlsx"/>
   </hyperlinks>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:L198"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="42" customWidth="1"/>
     <col min="2" max="2" width="25.375" style="42" customWidth="1"/>
@@ -3121,93 +3543,93 @@
     <col min="14" max="16384" width="9" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C1" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="47" t="s">
+      <c r="D1" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="47" t="s">
+      <c r="G1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="58" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="60"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="54"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47" t="s">
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="I2" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="J2" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="L2" s="50" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="85.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="47" t="s">
+    <row r="3" ht="85.5" customHeight="1" spans="1:12">
+      <c r="A3" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47" t="s">
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="47" t="s">
+      <c r="I3" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="47" t="s">
+      <c r="J3" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="47"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L3" s="50"/>
+    </row>
+    <row r="4" spans="2:10">
       <c r="B4" s="42" t="s">
         <v>51</v>
       </c>
@@ -3220,7 +3642,7 @@
       <c r="E4" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="52" t="s">
         <v>53</v>
       </c>
       <c r="I4" s="42" t="s">
@@ -3230,7 +3652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="8:10">
       <c r="H5" s="42" t="s">
         <v>55</v>
       </c>
@@ -3241,7 +3663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="8:10">
       <c r="H6" s="42" t="s">
         <v>57</v>
       </c>
@@ -3252,7 +3674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="8:10">
       <c r="H7" s="42" t="s">
         <v>59</v>
       </c>
@@ -3263,7 +3685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="8:10">
       <c r="H8" s="42" t="s">
         <v>61</v>
       </c>
@@ -3274,7 +3696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="8:10">
       <c r="H9" s="42" t="s">
         <v>63</v>
       </c>
@@ -3285,7 +3707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="8:10">
       <c r="H10" s="46" t="s">
         <v>65</v>
       </c>
@@ -3296,7 +3718,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="8:10">
       <c r="H11" s="42" t="s">
         <v>67</v>
       </c>
@@ -3307,7 +3729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="8:10">
       <c r="H12" s="42" t="s">
         <v>69</v>
       </c>
@@ -3318,7 +3740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="8:10">
       <c r="H13" s="42" t="s">
         <v>71</v>
       </c>
@@ -3329,7 +3751,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="8:10">
       <c r="H14" s="42" t="s">
         <v>73</v>
       </c>
@@ -3340,7 +3762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="8:10">
       <c r="H15" s="42" t="s">
         <v>75</v>
       </c>
@@ -3351,7 +3773,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="8:10">
       <c r="H16" s="42" t="s">
         <v>77</v>
       </c>
@@ -3362,7 +3784,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="8:10">
       <c r="H17" s="42" t="s">
         <v>79</v>
       </c>
@@ -3373,7 +3795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="8:10">
       <c r="H18" s="46" t="s">
         <v>81</v>
       </c>
@@ -3384,7 +3806,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="8:10">
       <c r="H19" s="46" t="s">
         <v>83</v>
       </c>
@@ -3395,7 +3817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:10">
       <c r="B21" s="42" t="s">
         <v>85</v>
       </c>
@@ -3418,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="8:10">
       <c r="H22" s="42" t="s">
         <v>88</v>
       </c>
@@ -3429,7 +3851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="8:10">
       <c r="H23" s="42" t="s">
         <v>90</v>
       </c>
@@ -3440,7 +3862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="8:10">
       <c r="H24" s="42" t="s">
         <v>92</v>
       </c>
@@ -3451,7 +3873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="8:10">
       <c r="H25" s="42" t="s">
         <v>94</v>
       </c>
@@ -3462,7 +3884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:10">
       <c r="B27" s="42" t="s">
         <v>96</v>
       </c>
@@ -3485,7 +3907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="8:10">
       <c r="H28" s="42" t="s">
         <v>92</v>
       </c>
@@ -3496,7 +3918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="8:10">
       <c r="H29" s="42" t="s">
         <v>94</v>
       </c>
@@ -3507,7 +3929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="8:10">
       <c r="H30" s="42" t="s">
         <v>100</v>
       </c>
@@ -3518,7 +3940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="8:10">
       <c r="H31" s="42" t="s">
         <v>102</v>
       </c>
@@ -3529,7 +3951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="8:10">
       <c r="H32" s="42" t="s">
         <v>104</v>
       </c>
@@ -3540,7 +3962,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:10">
       <c r="B35" s="42" t="s">
         <v>106</v>
       </c>
@@ -3560,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="8:10">
       <c r="H36" s="42" t="s">
         <v>107</v>
       </c>
@@ -3571,7 +3993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="8:10">
       <c r="H37" s="42" t="s">
         <v>109</v>
       </c>
@@ -3582,8 +4004,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="2:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="40" ht="23.25" customHeight="1"/>
+    <row r="41" spans="2:11">
       <c r="B41" s="42" t="s">
         <v>111</v>
       </c>
@@ -3606,7 +4028,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="8:11">
       <c r="H42" s="41" t="s">
         <v>114</v>
       </c>
@@ -3620,7 +4042,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="8:11">
       <c r="H43" s="42" t="s">
         <v>117</v>
       </c>
@@ -3634,7 +4056,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="8:11">
       <c r="H44" s="41" t="s">
         <v>120</v>
       </c>
@@ -3648,7 +4070,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="8:11">
       <c r="H45" s="42" t="s">
         <v>123</v>
       </c>
@@ -3662,7 +4084,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="8:11">
       <c r="H46" s="42" t="s">
         <v>126</v>
       </c>
@@ -3676,7 +4098,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="8:11">
       <c r="H47" s="42" t="s">
         <v>129</v>
       </c>
@@ -3690,7 +4112,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="8:10">
       <c r="H48" s="42" t="s">
         <v>132</v>
       </c>
@@ -3701,7 +4123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="8:10">
       <c r="H49" s="42" t="s">
         <v>134</v>
       </c>
@@ -3712,7 +4134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="8:10">
       <c r="H50" s="42" t="s">
         <v>136</v>
       </c>
@@ -3723,7 +4145,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="8:10">
       <c r="H51" s="42" t="s">
         <v>138</v>
       </c>
@@ -3734,7 +4156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="8:10">
       <c r="H52" s="42" t="s">
         <v>140</v>
       </c>
@@ -3745,7 +4167,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="8:10">
       <c r="H53" s="42" t="s">
         <v>142</v>
       </c>
@@ -3756,7 +4178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="8:10">
       <c r="H54" s="42" t="s">
         <v>144</v>
       </c>
@@ -3767,7 +4189,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="8:11">
       <c r="H55" s="42" t="s">
         <v>146</v>
       </c>
@@ -3781,7 +4203,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="8:11">
       <c r="H56" s="42" t="s">
         <v>149</v>
       </c>
@@ -3795,7 +4217,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="57" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="8:11">
       <c r="H57" s="42" t="s">
         <v>152</v>
       </c>
@@ -3809,7 +4231,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="58" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="8:11">
       <c r="H58" s="41" t="s">
         <v>155</v>
       </c>
@@ -3823,7 +4245,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="59" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="8:11">
       <c r="H59" s="42" t="s">
         <v>158</v>
       </c>
@@ -3837,7 +4259,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="60" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="8:11">
       <c r="H60" s="46" t="s">
         <v>161</v>
       </c>
@@ -3851,7 +4273,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="61" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="8:11">
       <c r="H61" s="42" t="s">
         <v>164</v>
       </c>
@@ -3865,7 +4287,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="62" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="8:11">
       <c r="H62" s="46" t="s">
         <v>167</v>
       </c>
@@ -3879,7 +4301,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="63" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="8:11">
       <c r="H63" s="46" t="s">
         <v>170</v>
       </c>
@@ -3893,7 +4315,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:10">
       <c r="B65" s="46" t="s">
         <v>172</v>
       </c>
@@ -3916,7 +4338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="8:10">
       <c r="H66" s="42" t="s">
         <v>173</v>
       </c>
@@ -3927,7 +4349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="8:10">
       <c r="H67" s="42" t="s">
         <v>175</v>
       </c>
@@ -3938,7 +4360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="8:10">
       <c r="H68" s="42" t="s">
         <v>177</v>
       </c>
@@ -3949,7 +4371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="8:10">
       <c r="H69" s="42" t="s">
         <v>179</v>
       </c>
@@ -3960,7 +4382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="8:10">
       <c r="H70" s="42" t="s">
         <v>181</v>
       </c>
@@ -3971,7 +4393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="8:10">
       <c r="H71" s="42" t="s">
         <v>183</v>
       </c>
@@ -3982,7 +4404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="8:10">
       <c r="H72" s="42" t="s">
         <v>185</v>
       </c>
@@ -3993,7 +4415,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="8:10">
       <c r="H73" s="42" t="s">
         <v>187</v>
       </c>
@@ -4004,7 +4426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="8:10">
       <c r="H74" s="42" t="s">
         <v>189</v>
       </c>
@@ -4015,7 +4437,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="8:10">
       <c r="H75" s="42" t="s">
         <v>191</v>
       </c>
@@ -4026,7 +4448,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="8:11">
       <c r="H76" s="42" t="s">
         <v>193</v>
       </c>
@@ -4040,7 +4462,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="8:11">
       <c r="H77" s="42" t="s">
         <v>196</v>
       </c>
@@ -4054,7 +4476,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="8:11">
       <c r="H78" s="42" t="s">
         <v>198</v>
       </c>
@@ -4068,7 +4490,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="8:11">
       <c r="H79" s="42" t="s">
         <v>200</v>
       </c>
@@ -4082,7 +4504,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="8:11">
       <c r="H80" s="42" t="s">
         <v>202</v>
       </c>
@@ -4096,7 +4518,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="81" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="8:11">
       <c r="H81" s="42" t="s">
         <v>205</v>
       </c>
@@ -4110,7 +4532,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="82" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="8:11">
       <c r="H82" s="42" t="s">
         <v>207</v>
       </c>
@@ -4124,7 +4546,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="83" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="8:11">
       <c r="H83" s="42" t="s">
         <v>210</v>
       </c>
@@ -4138,7 +4560,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="84" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="8:11">
       <c r="H84" s="42" t="s">
         <v>213</v>
       </c>
@@ -4152,7 +4574,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="85" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="8:11">
       <c r="H85" s="42" t="s">
         <v>215</v>
       </c>
@@ -4166,7 +4588,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="86" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="8:11">
       <c r="H86" s="42" t="s">
         <v>218</v>
       </c>
@@ -4180,7 +4602,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="87" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="8:10">
       <c r="H87" s="42" t="s">
         <v>220</v>
       </c>
@@ -4191,7 +4613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="8:11">
       <c r="H88" s="42" t="s">
         <v>222</v>
       </c>
@@ -4205,7 +4627,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="89" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="8:11">
       <c r="H89" s="42" t="s">
         <v>123</v>
       </c>
@@ -4219,7 +4641,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="90" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="8:11">
       <c r="H90" s="46" t="s">
         <v>142</v>
       </c>
@@ -4233,7 +4655,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="91" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="8:10">
       <c r="H91" s="42" t="s">
         <v>228</v>
       </c>
@@ -4244,7 +4666,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="92" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="8:11">
       <c r="H92" s="42" t="s">
         <v>230</v>
       </c>
@@ -4258,7 +4680,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="93" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="8:11">
       <c r="H93" s="42" t="s">
         <v>132</v>
       </c>
@@ -4272,7 +4694,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="94" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="8:11">
       <c r="H94" s="42" t="s">
         <v>134</v>
       </c>
@@ -4286,7 +4708,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="95" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="8:11">
       <c r="H95" s="42" t="s">
         <v>233</v>
       </c>
@@ -4300,7 +4722,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="96" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="8:11">
       <c r="H96" s="42" t="s">
         <v>144</v>
       </c>
@@ -4314,7 +4736,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="97" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="8:11">
       <c r="H97" s="42" t="s">
         <v>235</v>
       </c>
@@ -4328,7 +4750,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="98" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="8:11">
       <c r="H98" s="42" t="s">
         <v>237</v>
       </c>
@@ -4342,7 +4764,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="99" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="8:11">
       <c r="H99" s="42" t="s">
         <v>240</v>
       </c>
@@ -4356,7 +4778,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="100" spans="8:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" ht="28.5" customHeight="1" spans="8:11">
       <c r="H100" s="42" t="s">
         <v>243</v>
       </c>
@@ -4366,11 +4788,11 @@
       <c r="J100" s="42">
         <v>35</v>
       </c>
-      <c r="K100" s="50" t="s">
+      <c r="K100" s="55" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="101" spans="8:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" ht="42.75" customHeight="1" spans="8:11">
       <c r="H101" s="42" t="s">
         <v>129</v>
       </c>
@@ -4380,11 +4802,11 @@
       <c r="J101" s="42">
         <v>36</v>
       </c>
-      <c r="K101" s="50" t="s">
+      <c r="K101" s="55" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="102" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="8:11">
       <c r="H102" s="42" t="s">
         <v>248</v>
       </c>
@@ -4394,9 +4816,9 @@
       <c r="J102" s="42">
         <v>37</v>
       </c>
-      <c r="K102" s="50"/>
-    </row>
-    <row r="103" spans="8:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K102" s="55"/>
+    </row>
+    <row r="103" ht="42.75" customHeight="1" spans="8:11">
       <c r="H103" s="42" t="s">
         <v>152</v>
       </c>
@@ -4406,11 +4828,11 @@
       <c r="J103" s="42">
         <v>38</v>
       </c>
-      <c r="K103" s="50" t="s">
+      <c r="K103" s="55" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="104" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="8:11">
       <c r="H104" s="42" t="s">
         <v>252</v>
       </c>
@@ -4420,11 +4842,11 @@
       <c r="J104" s="42">
         <v>39</v>
       </c>
-      <c r="K104" s="50" t="s">
+      <c r="K104" s="55" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="105" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="8:11">
       <c r="H105" s="42" t="s">
         <v>254</v>
       </c>
@@ -4434,11 +4856,11 @@
       <c r="J105" s="42">
         <v>40</v>
       </c>
-      <c r="K105" s="50" t="s">
+      <c r="K105" s="55" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="106" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="8:11">
       <c r="H106" s="42" t="s">
         <v>257</v>
       </c>
@@ -4448,9 +4870,9 @@
       <c r="J106" s="42">
         <v>41</v>
       </c>
-      <c r="K106" s="50"/>
-    </row>
-    <row r="107" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="K106" s="55"/>
+    </row>
+    <row r="107" spans="8:11">
       <c r="H107" s="42" t="s">
         <v>259</v>
       </c>
@@ -4460,11 +4882,11 @@
       <c r="J107" s="42">
         <v>42</v>
       </c>
-      <c r="K107" s="50" t="s">
+      <c r="K107" s="55" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="108" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="8:11">
       <c r="H108" s="42" t="s">
         <v>261</v>
       </c>
@@ -4474,11 +4896,11 @@
       <c r="J108" s="42">
         <v>43</v>
       </c>
-      <c r="K108" s="50" t="s">
+      <c r="K108" s="55" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="109" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="8:11">
       <c r="H109" s="42" t="s">
         <v>264</v>
       </c>
@@ -4492,7 +4914,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="110" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="8:11">
       <c r="H110" s="42" t="s">
         <v>267</v>
       </c>
@@ -4506,7 +4928,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="111" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="8:11">
       <c r="H111" s="42" t="s">
         <v>269</v>
       </c>
@@ -4520,7 +4942,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="112" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="8:11">
       <c r="H112" s="42" t="s">
         <v>272</v>
       </c>
@@ -4534,7 +4956,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="113" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="8:11">
       <c r="H113" s="42" t="s">
         <v>275</v>
       </c>
@@ -4548,7 +4970,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="114" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="8:11">
       <c r="H114" s="42" t="s">
         <v>278</v>
       </c>
@@ -4562,7 +4984,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="115" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="8:11">
       <c r="H115" s="42" t="s">
         <v>281</v>
       </c>
@@ -4576,7 +4998,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="116" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="8:11">
       <c r="H116" s="42" t="s">
         <v>284</v>
       </c>
@@ -4590,7 +5012,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="117" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="8:10">
       <c r="H117" s="42" t="s">
         <v>286</v>
       </c>
@@ -4601,7 +5023,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="118" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="8:10">
       <c r="H118" s="42" t="s">
         <v>288</v>
       </c>
@@ -4612,7 +5034,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="119" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="8:11">
       <c r="H119" s="42" t="s">
         <v>290</v>
       </c>
@@ -4626,7 +5048,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="120" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="8:11">
       <c r="H120" s="42" t="s">
         <v>293</v>
       </c>
@@ -4640,7 +5062,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="121" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="8:11">
       <c r="H121" s="42" t="s">
         <v>296</v>
       </c>
@@ -4654,7 +5076,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="122" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="8:11">
       <c r="H122" s="42" t="s">
         <v>299</v>
       </c>
@@ -4665,7 +5087,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="123" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="8:11">
       <c r="H123" s="42" t="s">
         <v>301</v>
       </c>
@@ -4679,7 +5101,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="124" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="8:11">
       <c r="H124" s="46" t="s">
         <v>304</v>
       </c>
@@ -4693,7 +5115,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="125" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="8:11">
       <c r="H125" s="46" t="s">
         <v>307</v>
       </c>
@@ -4707,7 +5129,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="126" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="8:11">
       <c r="H126" s="46" t="s">
         <v>309</v>
       </c>
@@ -4721,7 +5143,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="127" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="8:11">
       <c r="H127" s="46" t="s">
         <v>312</v>
       </c>
@@ -4735,7 +5157,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="128" spans="8:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="8:11">
       <c r="H128" s="46" t="s">
         <v>314</v>
       </c>
@@ -4749,7 +5171,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="8:11">
       <c r="H129" s="46" t="s">
         <v>317</v>
       </c>
@@ -4763,7 +5185,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="8:11">
       <c r="H130" s="46" t="s">
         <v>320</v>
       </c>
@@ -4777,21 +5199,21 @@
         <v>322</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H131" s="54" t="s">
+    <row r="131" spans="8:11">
+      <c r="H131" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="I131" s="54" t="s">
+      <c r="I131" s="46" t="s">
         <v>324</v>
       </c>
       <c r="J131" s="42">
         <v>66</v>
       </c>
-      <c r="K131" s="54" t="s">
+      <c r="K131" s="46" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="8:10">
       <c r="H132" s="42" t="s">
         <v>326</v>
       </c>
@@ -4802,7 +5224,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:10">
       <c r="B137" s="42" t="s">
         <v>328</v>
       </c>
@@ -4825,7 +5247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="8:10">
       <c r="H138" s="42" t="s">
         <v>331</v>
       </c>
@@ -4836,7 +5258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:10">
       <c r="B142" s="42" t="s">
         <v>333</v>
       </c>
@@ -4859,7 +5281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="8:10">
       <c r="H143" s="42" t="s">
         <v>334</v>
       </c>
@@ -4870,7 +5292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="8:10">
       <c r="H144" s="42" t="s">
         <v>336</v>
       </c>
@@ -4881,7 +5303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:11">
       <c r="B146" s="42" t="s">
         <v>338</v>
       </c>
@@ -4897,7 +5319,7 @@
       <c r="H146" s="42" t="s">
         <v>339</v>
       </c>
-      <c r="I146" s="54" t="s">
+      <c r="I146" s="46" t="s">
         <v>340</v>
       </c>
       <c r="J146" s="42">
@@ -4907,11 +5329,11 @@
         <v>341</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="8:11">
       <c r="H147" s="42" t="s">
         <v>342</v>
       </c>
-      <c r="I147" s="54" t="s">
+      <c r="I147" s="46" t="s">
         <v>343</v>
       </c>
       <c r="J147" s="42">
@@ -4921,11 +5343,11 @@
         <v>344</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="8:11">
       <c r="H148" s="42" t="s">
         <v>345</v>
       </c>
-      <c r="I148" s="54" t="s">
+      <c r="I148" s="46" t="s">
         <v>346</v>
       </c>
       <c r="J148" s="42">
@@ -4935,21 +5357,21 @@
         <v>347</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H149" s="54" t="s">
+    <row r="149" spans="8:11">
+      <c r="H149" s="46" t="s">
         <v>348</v>
       </c>
-      <c r="I149" s="54" t="s">
+      <c r="I149" s="46" t="s">
         <v>349</v>
       </c>
       <c r="J149" s="42">
         <v>3</v>
       </c>
-      <c r="K149" s="54" t="s">
+      <c r="K149" s="46" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:11">
       <c r="B151" s="42" t="s">
         <v>351</v>
       </c>
@@ -4975,7 +5397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="8:11">
       <c r="H152" s="42" t="s">
         <v>155</v>
       </c>
@@ -4989,7 +5411,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="8:11">
       <c r="H153" s="46" t="s">
         <v>161</v>
       </c>
@@ -5003,7 +5425,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="8:11">
       <c r="H154" s="42" t="s">
         <v>149</v>
       </c>
@@ -5017,7 +5439,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="8:11">
       <c r="H155" s="42" t="s">
         <v>158</v>
       </c>
@@ -5031,7 +5453,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="8:11">
       <c r="H156" s="42" t="s">
         <v>114</v>
       </c>
@@ -5045,7 +5467,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="8:11">
       <c r="H157" s="42" t="s">
         <v>120</v>
       </c>
@@ -5059,7 +5481,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="8:11">
       <c r="H158" s="42" t="s">
         <v>129</v>
       </c>
@@ -5073,7 +5495,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="8:11">
       <c r="H159" s="42" t="s">
         <v>152</v>
       </c>
@@ -5087,7 +5509,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="8:10">
       <c r="H160" s="46" t="s">
         <v>353</v>
       </c>
@@ -5098,21 +5520,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H161" s="54" t="s">
+    <row r="161" spans="8:11">
+      <c r="H161" s="46" t="s">
         <v>355</v>
       </c>
-      <c r="I161" s="54" t="s">
+      <c r="I161" s="46" t="s">
         <v>356</v>
       </c>
       <c r="J161" s="42">
         <v>10</v>
       </c>
-      <c r="K161" s="54" t="s">
+      <c r="K161" s="46" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:11">
       <c r="B163" s="42" t="s">
         <v>358</v>
       </c>
@@ -5138,7 +5560,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="8:11">
       <c r="H164" s="42" t="s">
         <v>155</v>
       </c>
@@ -5152,7 +5574,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="8:11">
       <c r="H165" s="42" t="s">
         <v>161</v>
       </c>
@@ -5166,7 +5588,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="8:11">
       <c r="H166" s="46" t="s">
         <v>360</v>
       </c>
@@ -5180,7 +5602,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:10">
       <c r="B168" s="42" t="s">
         <v>362</v>
       </c>
@@ -5203,7 +5625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="8:10">
       <c r="H169" s="42" t="s">
         <v>365</v>
       </c>
@@ -5214,7 +5636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="8:10">
       <c r="H170" s="42" t="s">
         <v>367</v>
       </c>
@@ -5225,7 +5647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="8:10">
       <c r="H171" s="42" t="s">
         <v>369</v>
       </c>
@@ -5236,7 +5658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:10">
       <c r="B173" s="46" t="s">
         <v>371</v>
       </c>
@@ -5256,7 +5678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="8:10">
       <c r="H174" s="46" t="s">
         <v>372</v>
       </c>
@@ -5267,7 +5689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="8:10">
       <c r="H175" s="46" t="s">
         <v>126</v>
       </c>
@@ -5278,7 +5700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="8:10">
       <c r="H176" s="46" t="s">
         <v>374</v>
       </c>
@@ -5289,7 +5711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:10">
       <c r="B178" s="42" t="s">
         <v>376</v>
       </c>
@@ -5312,7 +5734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="8:10">
       <c r="H179" s="42" t="s">
         <v>378</v>
       </c>
@@ -5323,7 +5745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:10">
       <c r="B181" s="46" t="s">
         <v>380</v>
       </c>
@@ -5346,7 +5768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="182" spans="8:10">
       <c r="H182" s="46" t="s">
         <v>383</v>
       </c>
@@ -5357,7 +5779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:10">
       <c r="B184" s="46" t="s">
         <v>385</v>
       </c>
@@ -5380,7 +5802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="185" spans="8:10">
       <c r="H185" s="46" t="s">
         <v>107</v>
       </c>
@@ -5391,7 +5813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="186" spans="8:10">
       <c r="H186" s="46" t="s">
         <v>388</v>
       </c>
@@ -5402,7 +5824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:10">
       <c r="B188" s="46" t="s">
         <v>390</v>
       </c>
@@ -5425,7 +5847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="189" spans="8:10">
       <c r="H189" s="46" t="s">
         <v>393</v>
       </c>
@@ -5436,7 +5858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="190" spans="8:10">
       <c r="H190" s="46" t="s">
         <v>395</v>
       </c>
@@ -5447,7 +5869,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="191" spans="8:10">
       <c r="H191" s="46" t="s">
         <v>397</v>
       </c>
@@ -5458,7 +5880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="192" spans="8:10">
       <c r="H192" s="46" t="s">
         <v>399</v>
       </c>
@@ -5469,7 +5891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:10">
       <c r="B194" s="46" t="s">
         <v>401</v>
       </c>
@@ -5489,7 +5911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="195" spans="8:10">
       <c r="H195" s="46" t="s">
         <v>404</v>
       </c>
@@ -5500,7 +5922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:10">
       <c r="B197" s="46" t="s">
         <v>406</v>
       </c>
@@ -5520,7 +5942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="8:10">
       <c r="H198" s="46" t="s">
         <v>409</v>
       </c>
@@ -5535,15 +5957,16 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:P34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="25.875" customWidth="1"/>
     <col min="3" max="3" width="17.25" customWidth="1"/>
@@ -5554,7 +5977,7 @@
     <col min="13" max="14" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -5582,17 +6005,17 @@
       <c r="I1" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="61" t="s">
+      <c r="J1" s="48" t="s">
         <v>414</v>
       </c>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-    </row>
-    <row r="2" spans="1:16" s="39" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+    </row>
+    <row r="2" s="39" customFormat="1" spans="1:16">
       <c r="A2" s="43" t="s">
         <v>0</v>
       </c>
@@ -5616,8 +6039,8 @@
       <c r="M2" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="62" t="s">
-        <v>641</v>
+      <c r="N2" s="49" t="s">
+        <v>416</v>
       </c>
       <c r="O2" s="44" t="s">
         <v>8</v>
@@ -5626,7 +6049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="40" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" s="40" customFormat="1" spans="1:16">
       <c r="A3" s="45" t="s">
         <v>11</v>
       </c>
@@ -5636,17 +6059,17 @@
       <c r="C3" s="45"/>
       <c r="D3" s="45"/>
       <c r="E3" s="45" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F3" s="45"/>
       <c r="G3" s="45"/>
       <c r="H3" s="45"/>
       <c r="I3" s="45"/>
       <c r="J3" s="45" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K3" s="45" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M3" s="45" t="s">
         <v>18</v>
@@ -5657,7 +6080,7 @@
       </c>
       <c r="P3" s="45"/>
     </row>
-    <row r="4" spans="1:16" s="40" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" s="40" customFormat="1" ht="16.15" customHeight="1" spans="1:16">
       <c r="A4" s="45"/>
       <c r="B4" s="45"/>
       <c r="C4" s="45"/>
@@ -5674,10 +6097,10 @@
       <c r="O4" s="45"/>
       <c r="P4" s="45"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16">
       <c r="A5" s="42"/>
-      <c r="B5" s="54" t="s">
-        <v>419</v>
+      <c r="B5" s="46" t="s">
+        <v>420</v>
       </c>
       <c r="J5" s="42"/>
       <c r="K5" s="42"/>
@@ -5686,7 +6109,7 @@
       <c r="O5" s="42"/>
       <c r="P5" s="42"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6" s="42"/>
       <c r="B6" s="42"/>
       <c r="J6" s="42"/>
@@ -5696,7 +6119,7 @@
       <c r="O6" s="42"/>
       <c r="P6" s="42"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="A7" s="42"/>
       <c r="B7" s="42"/>
       <c r="C7" s="42"/>
@@ -5707,249 +6130,250 @@
       <c r="O7" s="42"/>
       <c r="P7" s="42"/>
     </row>
-    <row r="9" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="14.65" customHeight="1" spans="2:11">
       <c r="B9" s="42" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C9" s="42"/>
       <c r="E9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K9" s="42" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="14.65" customHeight="1" spans="2:11">
       <c r="B10" s="42"/>
       <c r="J10" s="42" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K10" s="42" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
       <c r="B11" s="42"/>
       <c r="C11" s="42"/>
       <c r="J11" s="42" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K11" s="42" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="12" ht="13.9" customHeight="1" spans="2:11">
       <c r="B12" s="42"/>
       <c r="J12" s="42"/>
       <c r="K12" s="42"/>
     </row>
-    <row r="13" spans="1:16" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="13.9" customHeight="1" spans="2:11">
       <c r="B13" s="42" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K13" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="10:11">
       <c r="J14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K14" s="42" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="15" spans="10:11">
       <c r="J15" s="42" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K15" s="42" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="16" spans="10:11">
       <c r="J16" s="42"/>
       <c r="K16" s="42"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11">
       <c r="B18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J18" s="42" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K18" s="42" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="10:11">
       <c r="J19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K19" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="10:11">
       <c r="J20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K20" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="10:11">
       <c r="J21" t="s">
+        <v>434</v>
+      </c>
+      <c r="K21" t="s">
         <v>433</v>
       </c>
-      <c r="K21" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="10:11">
       <c r="J23" s="42"/>
       <c r="K23" s="42"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11">
       <c r="B24" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E24" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G24" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K24" s="42" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="10:11">
       <c r="J25" s="42" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K25" s="42" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="26" spans="10:11">
       <c r="J26" s="42" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K26" s="42" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="27" spans="10:11">
       <c r="J27" s="42"/>
       <c r="K27" s="42"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B28" s="55" t="s">
-        <v>436</v>
+    <row r="28" spans="2:11">
+      <c r="B28" s="47" t="s">
+        <v>437</v>
       </c>
       <c r="C28" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E28" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G28" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J28" s="42" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K28" s="42" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="10:11">
       <c r="J29" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="K29" s="42" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" spans="10:11">
+      <c r="J30" s="42" t="s">
+        <v>426</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" t="s">
+        <v>439</v>
+      </c>
+      <c r="C32" t="s">
+        <v>420</v>
+      </c>
+      <c r="E32" t="s">
+        <v>422</v>
+      </c>
+      <c r="G32" t="s">
+        <v>440</v>
+      </c>
+      <c r="J32" s="42" t="s">
         <v>423</v>
-      </c>
-      <c r="K29" s="42" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="J30" s="42" t="s">
-        <v>425</v>
-      </c>
-      <c r="K30" s="42" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B32" t="s">
-        <v>438</v>
-      </c>
-      <c r="C32" t="s">
-        <v>419</v>
-      </c>
-      <c r="E32" t="s">
-        <v>421</v>
-      </c>
-      <c r="G32" t="s">
-        <v>439</v>
-      </c>
-      <c r="J32" s="42" t="s">
-        <v>422</v>
       </c>
       <c r="K32" s="42" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="10:11">
       <c r="J33" s="42" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K33" s="42" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="34" spans="10:11">
       <c r="J34" s="46" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K34" s="42" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="6.625" customWidth="1"/>
     <col min="3" max="3" width="27.5" customWidth="1"/>
@@ -5964,7 +6388,7 @@
     <col min="14" max="14" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" customHeight="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5972,169 +6396,169 @@
         <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>433</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" spans="1:14">
       <c r="A3" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" customHeight="1" spans="1:14">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>458</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="C4" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="E4" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="F4" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="G4" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="H4" s="9" t="s">
         <v>465</v>
       </c>
-      <c r="J4" s="37" t="s">
+      <c r="I4" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="J4" s="38" t="s">
         <v>467</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="K4" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="L4" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="M4" s="9" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N4" s="9" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" spans="1:14">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -6152,55 +6576,56 @@
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="38">
+    <row r="6" spans="2:14">
+      <c r="B6" s="37">
         <v>1001</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>471</v>
-      </c>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="37" t="s">
         <v>472</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="D6" s="37" t="s">
         <v>473</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="E6" s="37" t="s">
         <v>474</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="F6" s="37" t="s">
         <v>475</v>
       </c>
-      <c r="H6" s="38" t="s">
+      <c r="G6" s="37" t="s">
         <v>476</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="H6" s="37" t="s">
         <v>477</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="I6" s="37" t="s">
         <v>478</v>
       </c>
-      <c r="K6" s="38" t="s">
+      <c r="J6" s="37" t="s">
         <v>479</v>
       </c>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38">
+      <c r="K6" s="37" t="s">
+        <v>480</v>
+      </c>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37">
         <v>36301</v>
       </c>
-      <c r="N6" s="38">
+      <c r="N6" s="37">
         <v>31101</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:X27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="8.375" customWidth="1"/>
     <col min="3" max="3" width="14" style="7" customWidth="1"/>
@@ -6224,7 +6649,7 @@
     <col min="24" max="24" width="9.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" customHeight="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6232,164 +6657,164 @@
         <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:24">
       <c r="A2" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C2" s="10" t="s">
         <v>454</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>455</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>455</v>
+      <c r="E2" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="I2" s="29" t="s">
+        <v>456</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="K2" s="11" t="s">
         <v>500</v>
       </c>
+      <c r="K2" s="21" t="s">
+        <v>501</v>
+      </c>
       <c r="L2" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>501</v>
+        <v>500</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>502</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>376</v>
       </c>
       <c r="O2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="S2" s="21" t="s">
         <v>454</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="R2" s="56" t="s">
-        <v>454</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="U2" s="11" t="s">
+      <c r="T2" s="21" t="s">
         <v>503</v>
       </c>
-      <c r="V2" s="11" t="s">
-        <v>424</v>
-      </c>
-      <c r="W2" s="11" t="s">
-        <v>455</v>
+      <c r="U2" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="V2" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="W2" s="21" t="s">
+        <v>456</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" spans="1:24">
       <c r="A3" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="10"/>
+      <c r="C3" s="16"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -6398,103 +6823,103 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
       <c r="S3" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
     </row>
-    <row r="4" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" customHeight="1" spans="1:24">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>504</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="C4" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="D4" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="E4" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="F4" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="G4" s="26" t="s">
         <v>510</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="H4" s="26" t="s">
         <v>511</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="I4" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="J4" s="9" t="s">
         <v>513</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="K4" s="9" t="s">
         <v>514</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="L4" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="M4" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="O4" s="16" t="s">
+      <c r="N4" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="P4" s="16" t="s">
+      <c r="O4" s="17" t="s">
         <v>518</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="P4" s="17" t="s">
         <v>519</v>
       </c>
-      <c r="R4" s="57" t="s">
+      <c r="Q4" s="9" t="s">
         <v>520</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="R4" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="T4" s="28" t="s">
+      <c r="S4" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="U4" s="16" t="s">
+      <c r="T4" s="31" t="s">
         <v>523</v>
       </c>
-      <c r="V4" s="16" t="s">
+      <c r="U4" s="17" t="s">
         <v>524</v>
       </c>
-      <c r="W4" s="29" t="s">
+      <c r="V4" s="17" t="s">
         <v>525</v>
       </c>
-      <c r="X4" s="30" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W4" s="32" t="s">
+        <v>526</v>
+      </c>
+      <c r="X4" s="33" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" spans="2:24">
       <c r="B5" s="6"/>
-      <c r="C5" s="31"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -6517,94 +6942,95 @@
       <c r="W5" s="6"/>
       <c r="X5" s="6"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="34"/>
-      <c r="X6" s="35"/>
-    </row>
-    <row r="7" spans="1:24" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="34"/>
-      <c r="X7" s="35"/>
-    </row>
-    <row r="27" spans="11:11" x14ac:dyDescent="0.2">
-      <c r="K27" s="23"/>
+    <row r="6" spans="2:24">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="34"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="36"/>
+    </row>
+    <row r="7" ht="28.5" customHeight="1" spans="2:24">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="18"/>
+      <c r="T7" s="18"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="34"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="36"/>
+    </row>
+    <row r="27" spans="11:11">
+      <c r="K27" s="13"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="13" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="11" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="9" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="duplicateValues" dxfId="7" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="duplicateValues" dxfId="5" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="60"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="3" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
   </conditionalFormatting>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AL9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="25.875" customWidth="1"/>
     <col min="3" max="3" width="11.625" customWidth="1"/>
@@ -6636,237 +7062,237 @@
     <col min="38" max="38" width="22.875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" customHeight="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="AJ1" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="AK1" s="9" t="s">
+      <c r="AJ1" s="22" t="s">
         <v>557</v>
       </c>
-      <c r="AL1" s="9" t="s">
+      <c r="AK1" s="22" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="2" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL1" s="22" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:38">
       <c r="A2" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>453</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="P2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="AB2" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="AE2" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="AF2" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="AI2" s="21" t="s">
+        <v>566</v>
+      </c>
+      <c r="AJ2" s="23" t="s">
         <v>454</v>
       </c>
-      <c r="Q2" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="S2" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="V2" s="2" t="s">
+      <c r="AK2" s="23" t="s">
         <v>455</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="AL2" s="23" t="s">
         <v>454</v>
       </c>
-      <c r="X2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="AA2" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="AB2" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="AF2" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="AI2" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="AJ2" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="AK2" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="AL2" s="12" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" ht="16.5" customHeight="1" spans="1:38">
       <c r="A3" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -6880,32 +7306,32 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P3" s="2"/>
-      <c r="Q3" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="R3" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="S3" s="10" t="s">
-        <v>429</v>
+      <c r="Q3" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="R3" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="S3" s="16" t="s">
+        <v>430</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
@@ -6920,127 +7346,127 @@
       <c r="AG3" s="2"/>
       <c r="AH3" s="2"/>
       <c r="AI3" s="2"/>
-      <c r="AJ3" s="12"/>
-      <c r="AK3" s="12"/>
-      <c r="AL3" s="12"/>
-    </row>
-    <row r="4" spans="1:38" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AJ3" s="23"/>
+      <c r="AK3" s="23"/>
+      <c r="AL3" s="23"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" spans="1:38">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>567</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="B4" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="C4" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="F4" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="G4" s="9" t="s">
         <v>573</v>
       </c>
-      <c r="I4" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="J4" s="13" t="s">
+      <c r="H4" s="9" t="s">
         <v>574</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="I4" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>575</v>
       </c>
+      <c r="K4" s="9" t="s">
+        <v>576</v>
+      </c>
       <c r="L4" s="15" t="s">
-        <v>576</v>
-      </c>
-      <c r="M4" s="13" t="s">
         <v>577</v>
       </c>
-      <c r="N4" s="13" t="s">
+      <c r="M4" s="9" t="s">
         <v>578</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="N4" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="O4" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="Q4" s="13" t="s">
+      <c r="P4" s="9" t="s">
         <v>581</v>
       </c>
-      <c r="R4" s="13" t="s">
+      <c r="Q4" s="9" t="s">
         <v>582</v>
       </c>
-      <c r="S4" s="13" t="s">
+      <c r="R4" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="T4" s="13" t="s">
+      <c r="S4" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="T4" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="U4" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="W4" s="16" t="s">
-        <v>517</v>
-      </c>
-      <c r="X4" s="13" t="s">
+      <c r="V4" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="Y4" s="13" t="s">
+      <c r="W4" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="X4" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="Z4" s="13" t="s">
+      <c r="Y4" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="AA4" s="13" t="s">
+      <c r="Z4" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="AB4" s="13" t="s">
+      <c r="AA4" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="AC4" s="13" t="s">
+      <c r="AB4" s="9" t="s">
         <v>592</v>
       </c>
-      <c r="AD4" s="13" t="s">
+      <c r="AC4" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="AE4" s="13" t="s">
+      <c r="AD4" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="AF4" s="13" t="s">
+      <c r="AE4" s="9" t="s">
         <v>595</v>
       </c>
-      <c r="AG4" s="13" t="s">
+      <c r="AF4" s="9" t="s">
         <v>596</v>
       </c>
-      <c r="AH4" s="13" t="s">
+      <c r="AG4" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="AI4" s="13" t="s">
+      <c r="AH4" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="AJ4" s="17" t="s">
+      <c r="AI4" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="AK4" s="17" t="s">
+      <c r="AJ4" s="24" t="s">
         <v>600</v>
       </c>
-      <c r="AL4" s="17" t="s">
+      <c r="AK4" s="24" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="5" spans="1:38" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AL4" s="24" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="5" ht="49.5" customHeight="1" spans="1:38">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -7068,7 +7494,7 @@
       <c r="W5" s="6"/>
       <c r="X5" s="6"/>
       <c r="Y5" s="6" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="Z5" s="6"/>
       <c r="AA5" s="6"/>
@@ -7080,172 +7506,173 @@
       <c r="AG5" s="6"/>
       <c r="AH5" s="6"/>
       <c r="AI5" s="6"/>
-      <c r="AJ5" s="18"/>
-      <c r="AK5" s="18"/>
-      <c r="AL5" s="18"/>
-    </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
-      <c r="T6" s="19"/>
-      <c r="U6" s="19"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="19"/>
-      <c r="AF6" s="19"/>
-      <c r="AG6" s="19"/>
-      <c r="AH6" s="19"/>
-      <c r="AI6" s="19"/>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B7" s="22"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="19"/>
-      <c r="AF7" s="19"/>
-      <c r="AG7" s="19"/>
-      <c r="AH7" s="19"/>
-      <c r="AI7" s="19"/>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="20"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="23"/>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="23"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="23"/>
-      <c r="AG8" s="23"/>
-      <c r="AH8" s="23"/>
-      <c r="AI8" s="23"/>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B9" s="25"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="20"/>
-      <c r="AB9" s="23"/>
-      <c r="AC9" s="23"/>
-      <c r="AD9" s="23"/>
-      <c r="AE9" s="23"/>
-      <c r="AF9" s="23"/>
-      <c r="AG9" s="23"/>
-      <c r="AH9" s="23"/>
-      <c r="AI9" s="23"/>
+      <c r="AJ5" s="25"/>
+      <c r="AK5" s="25"/>
+      <c r="AL5" s="25"/>
+    </row>
+    <row r="6" spans="2:35">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="18"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="18"/>
+      <c r="AB6" s="11"/>
+      <c r="AC6" s="11"/>
+      <c r="AD6" s="11"/>
+      <c r="AE6" s="11"/>
+      <c r="AF6" s="11"/>
+      <c r="AG6" s="11"/>
+      <c r="AH6" s="11"/>
+      <c r="AI6" s="11"/>
+    </row>
+    <row r="7" spans="2:35">
+      <c r="B7" s="12"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="18"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="18"/>
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="11"/>
+      <c r="AD7" s="11"/>
+      <c r="AE7" s="11"/>
+      <c r="AF7" s="11"/>
+      <c r="AG7" s="11"/>
+      <c r="AH7" s="11"/>
+      <c r="AI7" s="11"/>
+    </row>
+    <row r="8" spans="2:35">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="18"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="13"/>
+      <c r="AH8" s="13"/>
+      <c r="AI8" s="13"/>
+    </row>
+    <row r="9" spans="2:35">
+      <c r="B9" s="14"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="14"/>
+      <c r="X9" s="14"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="18"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AH9" s="13"/>
+      <c r="AI9" s="13"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="C6:G9">
-    <cfRule type="duplicateValues" dxfId="1" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
     <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="14.25" customWidth="1"/>
     <col min="3" max="3" width="52.375" customWidth="1"/>
     <col min="4" max="4" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="16.5" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7254,44 +7681,44 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="16.5" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" spans="1:4">
       <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
@@ -7299,403 +7726,403 @@
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4">
       <c r="B6" s="7">
         <v>1001</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4">
       <c r="B7" s="7">
         <v>1002</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D7" s="7">
         <v>-3</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4">
       <c r="B8" s="7">
         <v>1003</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D8" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4">
       <c r="B9" s="7">
         <v>10001</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4">
       <c r="B10" s="7">
         <v>10002</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D10" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4">
       <c r="B11" s="7">
         <v>10003</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D11" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4">
       <c r="B12" s="7">
         <v>10004</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D12" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:4">
       <c r="B13" s="7">
         <v>10005</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D13" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:4">
       <c r="B14" s="7">
         <v>10006</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D14" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:4">
       <c r="B15" s="7">
         <v>10007</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D15" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:4">
       <c r="B16" s="7">
         <v>10008</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D16" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4">
       <c r="B17" s="7">
         <v>10009</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D17" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4">
       <c r="B18" s="7">
         <v>20000</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D18" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4">
       <c r="B19" s="7">
         <v>20001</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D19" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4">
       <c r="B20" s="7">
         <v>20002</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D20" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4">
       <c r="B21" s="7">
         <v>20009</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D21" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4">
       <c r="B22" s="7">
         <v>20013</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D22" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4">
       <c r="B23" s="7">
         <v>20014</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D23" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4">
       <c r="B24" s="7">
         <v>20015</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D24" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:4">
       <c r="B25" s="7">
         <v>40001</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D25" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4">
       <c r="B26" s="7">
         <v>40002</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D26" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4">
       <c r="B27" s="7">
         <v>40003</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D27" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4">
       <c r="B28" s="7">
         <v>40004</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D28" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:4">
       <c r="B29" s="7">
         <v>40005</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D29" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:4">
       <c r="B30" s="7">
         <v>50001</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D30" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:4">
       <c r="B31" s="7">
         <v>50002</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D31" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:4">
       <c r="B32" s="7">
         <v>50003</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D32" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4">
       <c r="B33" s="7">
         <v>50004</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D33" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:4">
       <c r="B34" s="7">
         <v>50005</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D34" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:4">
       <c r="B35" s="7">
         <v>41410</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D35" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:4">
       <c r="B36" s="7">
         <v>41210</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D36" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4">
       <c r="B37" s="7">
         <v>41213</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D37" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:4">
       <c r="B38" s="7">
         <v>11110</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D38" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:4">
       <c r="B39" s="7">
         <v>72000</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D39" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:4">
       <c r="B40" s="7">
         <v>10120</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D40" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:4">
       <c r="B41" s="7">
         <v>7002404</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D41" s="7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>